--- a/data/trans_dic/IP16A03-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A03-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
+          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,82</t>
+          <t>0,0; 22,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,76</t>
+          <t>0,0; 20,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,7</t>
+          <t>0,0; 8,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,19</t>
+          <t>0,0; 15,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,01</t>
+          <t>0,0; 15,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 28,12</t>
+          <t>3,18; 25,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,74</t>
+          <t>0,0; 6,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 12,64</t>
+          <t>1,42; 12,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 11,64</t>
+          <t>1,02; 10,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 15,38</t>
+          <t>1,73; 14,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,2</t>
+          <t>0,0; 5,08</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,25</t>
+          <t>0,0; 16,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,9</t>
+          <t>0,0; 14,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,96</t>
+          <t>0,0; 16,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,25</t>
+          <t>0,0; 18,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,95</t>
+          <t>0,0; 22,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,21</t>
+          <t>0,0; 12,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,27</t>
+          <t>0,0; 12,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 17,19</t>
+          <t>1,45; 16,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,82</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,36</t>
+          <t>0,0; 27,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,38</t>
+          <t>0,0; 28,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,62</t>
+          <t>0,0; 28,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 25,98</t>
+          <t>2,64; 26,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,31</t>
+          <t>0,0; 21,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,02</t>
+          <t>0,0; 33,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 21,04</t>
+          <t>3,53; 19,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,35</t>
+          <t>0,0; 19,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,55</t>
+          <t>0,0; 13,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,89</t>
+          <t>0,0; 21,35</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 16,18</t>
+          <t>1,83; 16,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 14,73</t>
+          <t>2,47; 14,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,23</t>
+          <t>0,0; 9,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,28</t>
+          <t>0,0; 7,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,85</t>
+          <t>0,0; 13,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 11,75</t>
+          <t>1,14; 13,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,32</t>
+          <t>0,0; 9,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,74</t>
+          <t>1,31; 11,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 10,62</t>
+          <t>1,83; 10,38</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 10,31</t>
+          <t>2,51; 10,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,61</t>
+          <t>0,74; 6,98</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,71</t>
+          <t>0,79; 6,57</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,7</t>
+          <t>0,0; 16,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,29</t>
+          <t>0,0; 15,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,06; 26,49</t>
+          <t>3,07; 26,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,43</t>
+          <t>0,0; 16,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,8</t>
+          <t>0,0; 15,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 17,82</t>
+          <t>2,95; 16,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,15</t>
+          <t>0,0; 7,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,8</t>
+          <t>0,0; 7,74</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,84</t>
+          <t>0,0; 6,97</t>
         </is>
       </c>
     </row>
@@ -1421,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,93</t>
+          <t>0,0; 39,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,82; 45,78</t>
+          <t>6,0; 46,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,8</t>
+          <t>0,0; 45,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,32</t>
+          <t>0,0; 31,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,64; 34,64</t>
+          <t>3,87; 34,5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,52</t>
+          <t>0,0; 13,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,07</t>
+          <t>0,0; 21,65</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,14</t>
+          <t>0,0; 19,81</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 10,32</t>
+          <t>3,11; 10,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 8,02</t>
+          <t>2,25; 8,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,03</t>
+          <t>0,6; 4,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 4,4</t>
+          <t>0,43; 4,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,36; 11,85</t>
+          <t>4,18; 11,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,74</t>
+          <t>1,37; 7,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 9,4</t>
+          <t>2,26; 9,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,57</t>
+          <t>1,64; 7,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,64; 9,67</t>
+          <t>4,46; 9,75</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,6</t>
+          <t>2,38; 6,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,82</t>
+          <t>2,11; 6,14</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,39</t>
+          <t>1,32; 4,33</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1190</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1827</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1718</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1837</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1827</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>812</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3378</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4386</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2172</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3362</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3488</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>565; 4511</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1887</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>521; 4681</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>439; 4693</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>582; 4826</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2859</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1860</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3218</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2020</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3220</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4201</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4813</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4365</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>452; 5110</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2126</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1926</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3239</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1926</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3079</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3115</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2533</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>580; 5858</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2654</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5818</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1166; 6601</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4640</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2569</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5740</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2537</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1471</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1534</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2301</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3910</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5837</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2061</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3835</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>688; 6201</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1204; 7042</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4509</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5566</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5194</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>670; 7899</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3424</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>731; 6331</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1396; 7941</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2696; 11304</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>596; 5658</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1046; 8681</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2831</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1318</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3459</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1318</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3161</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4560</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>734; 6441</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4586</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4004</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1262; 6976</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4095</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4049</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4523</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2242</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1496</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1463</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2859</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1496</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1463</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2582</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2792</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>680; 5291</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4480</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4801</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>728; 6492</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2835</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4937</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5453</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>6564</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2896</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>9834</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>6081</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>16448</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>11747</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>8590</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>8977</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>3418; 11300</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3138; 11283</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>741; 5776</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>761; 7522</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5650; 16011</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2006; 10290</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2647; 11034</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2944; 12656</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>10933; 23884</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>6796; 18188</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5059; 14721</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>4683; 15363</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A03-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A03-Clase-trans_dic.xlsx
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,26</t>
+          <t>0,0; 26,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,97</t>
+          <t>0,0; 20,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,42 +732,42 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,74</t>
+          <t>0,0; 11,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,67</t>
+          <t>0,0; 11,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,87</t>
+          <t>0,0; 12,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 25,42</t>
+          <t>3,27; 27,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,01</t>
+          <t>0,0; 6,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 12,78</t>
+          <t>1,43; 13,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 10,94</t>
+          <t>1,0; 11,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 14,37</t>
+          <t>1,74; 13,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,29</t>
+          <t>0,0; 13,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,05</t>
+          <t>0,0; 14,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,84</t>
+          <t>0,0; 20,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,03</t>
+          <t>0,0; 18,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,04</t>
+          <t>0,0; 25,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,91</t>
+          <t>0,0; 11,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,47</t>
+          <t>0,0; 12,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 16,45</t>
+          <t>1,43; 16,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,17 +997,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,71</t>
+          <t>0,0; 31,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,34</t>
+          <t>0,0; 28,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,64</t>
+          <t>0,0; 22,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 26,69</t>
+          <t>2,63; 23,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,27</t>
+          <t>0,0; 21,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,64</t>
+          <t>0,0; 35,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 19,96</t>
+          <t>3,46; 21,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,77</t>
+          <t>0,0; 20,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,44</t>
+          <t>0,0; 12,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,35</t>
+          <t>0,0; 23,26</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 16,45</t>
+          <t>1,95; 17,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 14,48</t>
+          <t>2,14; 14,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,7</t>
+          <t>0,0; 11,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,29</t>
+          <t>0,0; 7,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,39</t>
+          <t>0,0; 12,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 13,41</t>
+          <t>1,13; 12,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,92</t>
+          <t>0,0; 10,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 11,34</t>
+          <t>1,07; 10,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 10,38</t>
+          <t>1,8; 10,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 10,51</t>
+          <t>1,96; 10,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,98</t>
+          <t>0,73; 7,07</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,57</t>
+          <t>0,86; 6,54</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,77</t>
+          <t>0,0; 19,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1292,22 +1292,22 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,78</t>
+          <t>0,0; 13,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,07; 26,95</t>
+          <t>3,05; 24,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,72</t>
+          <t>0,0; 16,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,6</t>
+          <t>0,0; 19,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 16,32</t>
+          <t>2,99; 17,52</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,3</t>
+          <t>0,0; 7,54</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,74</t>
+          <t>0,0; 7,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,97</t>
+          <t>0,0; 6,11</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,5</t>
+          <t>0,0; 35,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,56</t>
+          <t>0,0; 39,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 46,67</t>
+          <t>5,89; 45,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1447,32 +1447,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,81</t>
+          <t>0,0; 43,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,38</t>
+          <t>0,0; 28,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,87; 34,5</t>
+          <t>4,65; 37,06</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,6</t>
+          <t>0,0; 17,37</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,65</t>
+          <t>0,0; 21,08</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,81</t>
+          <t>0,0; 17,74</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,11; 10,3</t>
+          <t>3,14; 10,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 8,11</t>
+          <t>2,36; 8,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,7</t>
+          <t>0,56; 4,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,29</t>
+          <t>0,48; 4,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,18; 11,83</t>
+          <t>4,32; 12,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 7,02</t>
+          <t>1,38; 7,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 9,43</t>
+          <t>2,37; 9,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 7,06</t>
+          <t>1,56; 6,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,46; 9,75</t>
+          <t>4,33; 9,48</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,36</t>
+          <t>2,33; 6,42</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,14</t>
+          <t>1,91; 5,78</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,33</t>
+          <t>1,33; 4,49</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3378</t>
+          <t>0; 4016</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4386</t>
+          <t>0; 4356</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1942,47 +1942,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2172</t>
+          <t>0; 2800</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3362</t>
+          <t>0; 2532</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3488</t>
+          <t>0; 2772</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>565; 4511</t>
+          <t>580; 4805</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1887</t>
+          <t>0; 2046</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>521; 4681</t>
+          <t>525; 4868</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>439; 4693</t>
+          <t>427; 4836</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>582; 4826</t>
+          <t>584; 4442</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2859</t>
+          <t>0; 2856</t>
         </is>
       </c>
     </row>
@@ -2135,17 +2135,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3165</t>
+          <t>0; 2596</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3218</t>
+          <t>0; 3365</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2020</t>
+          <t>0; 2473</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3220</t>
+          <t>0; 3309</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4201</t>
+          <t>0; 4893</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2175,17 +2175,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4813</t>
+          <t>0; 4413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4365</t>
+          <t>0; 4339</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>452; 5110</t>
+          <t>444; 5045</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2343,17 +2343,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3079</t>
+          <t>0; 3525</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3115</t>
+          <t>0; 3118</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2533</t>
+          <t>0; 2017</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>580; 5858</t>
+          <t>578; 5228</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2654</t>
+          <t>0; 2639</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,27 +2378,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5818</t>
+          <t>0; 6053</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1166; 6601</t>
+          <t>1143; 7147</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4640</t>
+          <t>0; 4715</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2569</t>
+          <t>0; 2455</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 5740</t>
+          <t>0; 6255</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>688; 6201</t>
+          <t>735; 6476</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1204; 7042</t>
+          <t>1043; 7245</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4509</t>
+          <t>0; 5175</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5566</t>
+          <t>0; 5884</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5194</t>
+          <t>0; 4926</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>670; 7899</t>
+          <t>668; 7179</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3424</t>
+          <t>0; 3519</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>731; 6331</t>
+          <t>598; 5689</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1396; 7941</t>
+          <t>1376; 7954</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2696; 11304</t>
+          <t>2108; 11092</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>596; 5658</t>
+          <t>588; 5731</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1046; 8681</t>
+          <t>1137; 8654</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3161</t>
+          <t>0; 3617</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2774,22 +2774,22 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4560</t>
+          <t>0; 3804</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>734; 6441</t>
+          <t>728; 5888</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4586</t>
+          <t>0; 4632</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4004</t>
+          <t>0; 4926</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2799,22 +2799,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1262; 6976</t>
+          <t>1279; 7488</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 4095</t>
+          <t>0; 4229</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4049</t>
+          <t>0; 3848</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 4523</t>
+          <t>0; 3966</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2582</t>
+          <t>0; 2632</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2792</t>
+          <t>0; 2799</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>680; 5291</t>
+          <t>667; 5207</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2997,32 +2997,32 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4480</t>
+          <t>0; 4235</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4801</t>
+          <t>0; 4379</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>728; 6492</t>
+          <t>876; 6975</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 2835</t>
+          <t>0; 3622</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 4937</t>
+          <t>0; 4808</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 5453</t>
+          <t>0; 4882</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3418; 11300</t>
+          <t>3448; 11222</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3138; 11283</t>
+          <t>3281; 11962</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>741; 5776</t>
+          <t>692; 5914</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>761; 7522</t>
+          <t>840; 7660</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5650; 16011</t>
+          <t>5846; 16253</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2006; 10290</t>
+          <t>2027; 10554</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2647; 11034</t>
+          <t>2775; 11307</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2944; 12656</t>
+          <t>2792; 12140</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10933; 23884</t>
+          <t>10618; 23217</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6796; 18188</t>
+          <t>6667; 18363</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5059; 14721</t>
+          <t>4578; 13863</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4683; 15363</t>
+          <t>4719; 15942</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A03-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP16A03-Clase-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10,3%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>7,25%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5,69%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,3%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,47</t>
+          <t>0,0; 14,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,82</t>
+          <t>0,0; 15,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>3,16; 28,12</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,27</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 26,82</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 19,76</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,27</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,8</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 12,61</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3,27; 27,08</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,52</t>
+          <t>0,0; 7,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 13,29</t>
+          <t>1,41; 12,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 11,27</t>
+          <t>1,02; 11,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 13,22</t>
+          <t>1,71; 15,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,08</t>
+          <t>0,0; 4,63</t>
         </is>
       </c>
     </row>
@@ -789,37 +789,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>3,19%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,19%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>3,79%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,36</t>
+          <t>0,0; 19,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,62</t>
+          <t>0,0; 21,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,37 +877,37 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,53</t>
+          <t>0,0; 14,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 13,9</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 16,96</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 25,67</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,84</t>
+          <t>0,0; 12,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,4</t>
+          <t>0,0; 11,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 16,24</t>
+          <t>1,5; 17,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -929,44 +929,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,69%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8,34%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>10,02%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6,35%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5,14%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>9,8%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,73</t>
+          <t>2,65; 25,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,37</t>
+          <t>0,0; 26,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 28,25</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 28,36</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 31,38</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 22,62</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2,63; 23,82</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 21,15</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 35,0</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 21,62</t>
+          <t>3,37; 21,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,09</t>
+          <t>0,0; 17,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,84</t>
+          <t>0,0; 12,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,26</t>
+          <t>0,0; 16,5</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6,73%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,72%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 17,19</t>
+          <t>0,0; 10,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 14,89</t>
+          <t>1,12; 11,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,13</t>
+          <t>0,0; 10,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,7</t>
+          <t>1,19; 11,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,7</t>
+          <t>1,81; 16,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 12,19</t>
+          <t>2,48; 14,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,19</t>
+          <t>0,0; 11,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,19</t>
+          <t>0,0; 13,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 10,4</t>
+          <t>1,82; 10,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 10,31</t>
+          <t>2,37; 10,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,07</t>
+          <t>0,71; 6,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 6,54</t>
+          <t>1,63; 9,07</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11,85%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,33%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>11,85%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,19</t>
+          <t>3,06; 26,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 15,43</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 20,8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 16,7</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,16</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,05; 24,64</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 16,89</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 13,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 17,52</t>
+          <t>3,13; 17,82</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,54</t>
+          <t>0,0; 8,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,36</t>
+          <t>0,0; 8,8</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,11</t>
+          <t>0,0; 5,11</t>
         </is>
       </c>
     </row>
@@ -1349,44 +1349,44 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19,78%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10,4%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>8,24%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>9,61%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19,78%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9,57%</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t>15,19%</t>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,17</t>
+          <t>5,82; 45,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 42,8</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 33,48</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 34,5</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 49,93</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>5,89; 45,93</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 43,31</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 28,62</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,65; 37,06</t>
+          <t>6,64; 34,64</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,37</t>
+          <t>0,0; 16,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,08</t>
+          <t>0,0; 21,07</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,74</t>
+          <t>0,0; 17,27</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>6,03%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>4,72%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1,94%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,14; 10,23</t>
+          <t>4,36; 11,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 8,6</t>
+          <t>1,35; 6,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,82</t>
+          <t>2,61; 9,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,37</t>
+          <t>1,49; 6,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,32; 12,01</t>
+          <t>3,13; 10,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,2</t>
+          <t>2,1; 8,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,37; 9,66</t>
+          <t>0,59; 5,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,77</t>
+          <t>0,45; 4,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,33; 9,48</t>
+          <t>4,64; 9,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,42</t>
+          <t>2,3; 6,6</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,78</t>
+          <t>1,91; 5,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,49</t>
+          <t>1,37; 4,45</t>
         </is>
       </c>
     </row>
@@ -1669,13 +1669,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,37 +1791,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1859,62 +1859,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1827</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1190</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1718</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1837</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>1827</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1718</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1837</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1827</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>689</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4016</t>
+          <t>0; 3046</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4356</t>
+          <t>0; 3299</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>561; 4990</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1809</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4069</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4134</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2800</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2532</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2772</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>580; 4805</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>0; 1839</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>525; 4868</t>
+          <t>517; 4632</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>427; 4836</t>
+          <t>437; 4992</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>584; 4442</t>
+          <t>573; 5165</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2856</t>
+          <t>0; 2478</t>
         </is>
       </c>
     </row>
@@ -2004,32 +2004,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2067,37 +2067,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>620</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>731</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>455</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1405</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2135,17 +2135,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2596</t>
+          <t>0; 3438</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3365</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2473</t>
+          <t>0; 4185</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2155,37 +2155,37 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3309</t>
+          <t>0; 2769</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>0; 3184</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2035</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4893</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4413</t>
+          <t>0; 4553</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 4339</t>
+          <t>0; 3944</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>444; 5045</t>
+          <t>465; 5340</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,44 +2275,44 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2126</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1254</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1113</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>698</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>455</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2126</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1926</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
           <t>3239</t>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1254</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3525</t>
+          <t>582; 5703</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3118</t>
+          <t>0; 3283</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2017</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0; 4244</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3151</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3449</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2001</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>578; 5228</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2639</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0; 6053</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1143; 7147</t>
+          <t>1115; 6957</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4715</t>
+          <t>0; 4073</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 2455</t>
+          <t>0; 2398</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 6255</t>
+          <t>0; 4049</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2569</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2124</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2537</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3268</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1471</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1534</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1374</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2569</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>3705</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>735; 6476</t>
+          <t>0; 4210</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1043; 7245</t>
+          <t>660; 6924</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5175</t>
+          <t>0; 3564</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5884</t>
+          <t>591; 5934</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4926</t>
+          <t>682; 6096</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>668; 7179</t>
+          <t>1206; 7163</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3519</t>
+          <t>0; 5219</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>598; 5689</t>
+          <t>0; 5608</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1376; 7954</t>
+          <t>1389; 8123</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2108; 11092</t>
+          <t>2548; 11084</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>588; 5731</t>
+          <t>576; 5351</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1137; 8654</t>
+          <t>1507; 8375</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,62 +2691,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2831</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1318</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2831</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3459</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>1318</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>891</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3459</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1318</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>891</t>
-        </is>
-      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>645</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3617</t>
+          <t>732; 6330</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>0; 4231</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5337</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3149</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0; 3804</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>728; 5888</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0; 4632</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3969</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1279; 7488</t>
+          <t>1337; 7620</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 4229</t>
+          <t>0; 4570</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 3848</t>
+          <t>0; 4600</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3966</t>
+          <t>0; 3108</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,62 +2899,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2242</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1496</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>616</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>678</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2242</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2859</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>1496</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1463</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2859</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1496</t>
-        </is>
-      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1468</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2632</t>
+          <t>660; 5190</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2799</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>0; 4185</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4725</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2582</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3523</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>667; 5207</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>0; 4235</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0; 4379</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>876; 6975</t>
+          <t>1249; 6520</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 3622</t>
+          <t>0; 3444</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 4808</t>
+          <t>0; 4804</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 4882</t>
+          <t>0; 4587</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>9834</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>6614</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>6564</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>2380</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2896</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>9834</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>5183</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>6210</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>7761</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3448; 11222</t>
+          <t>5903; 16034</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3281; 11962</t>
+          <t>1983; 9881</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>692; 5914</t>
+          <t>3049; 11006</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>840; 7660</t>
+          <t>2417; 10294</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5846; 16253</t>
+          <t>3435; 11327</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2027; 10554</t>
+          <t>2918; 11164</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2775; 11307</t>
+          <t>727; 6177</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2792; 12140</t>
+          <t>635; 6455</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10618; 23217</t>
+          <t>11359; 23691</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6667; 18363</t>
+          <t>6580; 18875</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4578; 13863</t>
+          <t>4591; 13966</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4719; 15942</t>
+          <t>4165; 13510</t>
         </is>
       </c>
     </row>
